--- a/hira_material_automation/output/monthly/202601_202604__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-04T21:37:55</t>
+          <t>2026-04-14T21:55:54</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>d756de95f41c1a5bd01a9b24c1fd1134793dd0a1282c3f511ea3ae8ec432f60b</t>
+          <t>5b688602815d6fef0b1d90ca8e39ec9d0f64cf9860817fc8ce2899b0181935e8</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202604__acl_interference_screw_absorbable__040012__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__acl_interference_screw_absorbable__040012__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14T21:55:54</t>
+          <t>2026-04-24T21:54:09</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5b688602815d6fef0b1d90ca8e39ec9d0f64cf9860817fc8ce2899b0181935e8</t>
+          <t>4b7d4981ff1f93f7b9c5ebe1a48394f9850e8633745203cdecb7052cacf66e52</t>
         </is>
       </c>
     </row>
